--- a/annotators/team/tg/de/annotated_both/ard.27823.xlsx
+++ b/annotators/team/tg/de/annotated_both/ard.27823.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\de\in-progress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\de\annotated_both\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A23B54-505F-4135-B7EA-6482873B615C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489E2ACE-8831-4A73-865E-E75AE1927ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15768" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15576" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sentence-level annotation" sheetId="1" r:id="rId1"/>
